--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -637,6 +637,25 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Minimum Depth of Binary Tree
+Walking Robot Simulation II</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,28 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Add Binary
+Combinations
+Insert Interval
+Remove Duplicates from Sorted List II
+XOR After Range Multiplication Queries I</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -678,6 +678,25 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Gray Code
+XOR After Range Multiplication Queries II</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -697,6 +697,25 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Flatten Binary Tree to Linked List
+Minimum Distance Between Three Equal Elements I</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -716,6 +716,27 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>46123</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>4</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>First Missing Positive
+Maximum Number of Events That Can Be Attended
+Minimum Depth of Binary Tree
+Minimum Distance Between Three Equal Elements II</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -737,6 +737,24 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>46124</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Minimum Distance to Type a Word Using Two Fingers</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -755,6 +755,25 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Climbing Stairs
+Minimum Distance to the Target Element</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -774,6 +774,25 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>House Robber
+Minimum Total Distance Traveled</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -793,6 +793,24 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Shortest Distance to Target String in a Circular Array</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -811,6 +811,24 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Closest Equal Element Queries</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -829,6 +829,24 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>46131</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Maximum Distance Between a Pair of Values</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -847,6 +847,24 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Check if There is a Valid Path in a Grid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -865,6 +865,25 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>2</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Minimum Operations to Make a Uni-Value Grid
+Populating Next Right Pointers in Each Node</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -884,6 +884,24 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Top K Frequent Elements</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -902,6 +902,24 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Maximum Path Score in a Grid</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -920,6 +920,24 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Rotate Function</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -938,6 +938,29 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>6</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Count Primes
+Final Value of Variable After Performing Operations
+Find First and Last Position of Element in Sorted Array
+Rotate Image
+Surrounded Regions
+Unique Paths</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D28"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -961,6 +961,42 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Rotate List</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rotating the Box</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -997,6 +997,24 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LRU Cache</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1015,6 +1015,26 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Corporate Flight Bookings
+Maximum Population Year
+Minimum Moves to Make Array Complementary</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1035,6 +1035,27 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>4</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Check if Array is Good
+Count Islands With Total Value Divisible by K
+Find Champion II
+Largest Triangle Area</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1056,6 +1056,25 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Find Minimum in Rotated Sorted Array
+Iterator for Combination</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1075,6 +1075,24 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Find Minimum in Rotated Sorted Array II</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,24 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Sunday</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Jump Game III</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D36"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1111,6 +1111,43 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Monday</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Jump Game IV</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Check Adjacent Digit Differences
+Minimum Common Value</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1148,6 +1148,24 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>1</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Find the Prefix Common Array of Two Arrays</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1166,6 +1166,24 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>1</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Find the Length of the Longest Common Prefix</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1184,6 +1184,24 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Search in Rotated Sorted Array</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1202,6 +1202,24 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Saturday</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>1</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Check if Array Is Sorted and Rotated</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1220,6 +1220,24 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>1</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Repeated DNA Sequences</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/leetcode_log.xlsx
+++ b/data/leetcode_log.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1238,6 +1238,24 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Wednesday</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Count the Number of Special Characters II</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
